--- a/client-docs/test-cases/emg-o-test-cases-e2e-mode1.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-e2e-mode1.xlsx
@@ -13,6 +13,8 @@
     <sheet name="E3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="E4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="E5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="E6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="E7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:D13"/>
+  <dimension ref="C2:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="2" max="2"/>
@@ -485,14 +487,14 @@
     <row r="5">
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Total test cases: 13</t>
+          <t>Total test cases: 15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>High / Medium / Low: 9 / 4 / 0</t>
+          <t>High / Medium / Low: 9 / 6 / 0</t>
         </is>
       </c>
     </row>
@@ -555,7 +557,27 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>E6 — สรุปกำไร (Gross Margin)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>E7 — ต้นทุนแยกตามมิติ (Cost-by-Material Analytics)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -668,29 +690,29 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>มี Vendor อยู่แล้วในระบบ (หรือสร้างใหม่ได้)</t>
+          <t>มี Material/Block Product พร้อมแล้ว (ดู Test Cases: Product/Material Setup) และมี Vendor อยู่แล้วในระบบ</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>1. เปิด Purchase &gt; Orders &gt; New
 2. เลือก Vendor
-3. เพิ่มบรรทัด เลือกสินค้า Block ของวัสดุที่ต้องการ (เช่น "Bianco Sardo Granite - Block")
+3. เพิ่มบรรทัด เลือกสินค้า Block ของวัสดุที่ต้องการ
 4. กรอกจำนวน (หน่วยเป็น m³) และราคาต่อหน่วย
 5. กด Confirm Order</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Vendor = "ทดสอบ E2E - Test Quarry Vendor"
-สินค้า = Bianco Sardo Granite - Block
-จำนวน = 8.5 m³
-ราคา/หน่วย = 18,000</t>
+          <t>Vendor = "Demo Supplier - Global Stone Quarry"
+สินค้า = SY-TST-Onyx-Rosa - Block
+จำนวน = 2.00 m³
+ราคา/หน่วย = 15,000</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>PO ยืนยันสำเร็จ (state = Purchase Order) ยอดรวมคำนวณถูกต้อง (จำนวน × ราคา + VAT) — ตัวอย่างจริงที่ทดสอบ: P00039 ยอดรวม 163,710</t>
+          <t>PO ยืนยันสำเร็จ (state = Purchase Order) ยอดรวมคำนวณถูกต้อง (จำนวน × ราคา + VAT) — ตัวอย่างจริงที่ทดสอบ: P00052 ยอดรวม 32,100.00</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -712,7 +734,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>สร้าง Block (Bundle) ผูกกับ PO — ขั้นตอนนี้คือการรับสต๊อกจริง</t>
+          <t>สร้าง Block (Bundle) ผ่านปุ่มลัด "สร้าง Block" บนบรรทัด PO</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -722,25 +744,21 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Stone Slab &gt; Blocks &gt; New
-2. เลือก Material (ต้องตรงกับสินค้าใน PO)
-3. เลือก Warehouse
-4. ที่ช่อง Purchase Order Line เลือก PO Line ที่เพิ่งสร้าง
-5. กรอก Total CBM (ตรงกับจำนวนใน PO) และ Thickness (M)
-6. กด Save</t>
+          <t>1. บนบรรทัดของ PO ที่เพิ่งยืนยัน กดปุ่ม "สร้าง Block"
+2. ฟอร์มสร้าง Block เปิดขึ้นพร้อมกรอก Material/Supplier/Warehouse/Total CBM ให้แล้ว
+3. กรอก Thickness (M) เพิ่ม
+4. กด Save</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Material = Bianco Sardo Granite
-Purchase Order Line = P00039 (บรรทัด Block)
-Total CBM = 8.5
-Thickness (M) = 0.02</t>
+          <t>Thickness (M) = 0.02
+(Total CBM/Material/Supplier/Warehouse กรอกมาให้แล้วจาก PO)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>บันทึกสำเร็จ ได้เลขก้อนอัตโนมัติ (เช่น BLK-26-0016) ช่อง "PO Cost / CBM" ขึ้นราคาต่อหน่วยจาก PO ให้เอง (18,000) — เปิด Inventory &gt; Blocks/Stone Available ดูจะเห็นสต๊อกก้อนนี้เข้ามาแล้วเท่ากับ Total CBM ที่กรอก</t>
+          <t>บันทึกสำเร็จ ได้เลขก้อนอัตโนมัติ (ตัวอย่างจริง: BLK-26-0068) ช่อง "PO Cost / CBM" ขึ้น 15,000 ให้เอง, "Sales Price / CBM" ขึ้น 17,500 ให้เองจาก List Price ของ Block Product, Remaining CBM = 2.00 (รับสต๊อกเข้าจริงแล้ว)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -750,7 +768,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>หมายเหตุ: ไม่มีขั้นตอน "Validate Receipt" แยกต่างหาก — การกด Save ที่นี่คือการรับของเข้าคลังเลย ใบรับสินค้า (Receipt) ที่ระบบสร้างให้อัตโนมัติจาก PO จะถูกยกเลิกให้เองเบื้องหลัง (กันสต๊อกซ้ำ) ไม่ต้องไปกดอะไรกับมัน</t>
+          <t>✨ ใหม่ (2026-09-09): ไม่ต้องเปิด Inventory &gt; Blocks &gt; New แล้วไปหา PO Line เองอีกต่อไป — กดปุ่มนี้ตรงบรรทัด PO ได้เลย ระบบกรอก Material/Supplier/Warehouse/Total CBM ให้อัตโนมัติจากบรรทัดนั้น ยังคงไม่มีขั้นตอน "Validate Receipt" แยกต่างหาก — Receipt ที่ระบบสร้างให้อัตโนมัติจาก PO จะถูกยกเลิกให้เองเบื้องหลัง (กันสต๊อกซ้ำ) ไม่ต้องไปกดอะไรกับมัน</t>
         </is>
       </c>
       <c r="I5" s="7" t="n"/>
@@ -776,20 +794,22 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด PO ที่สร้างไว้
-2. กดปุ่ม "Create Bill"
-3. ตรวจยอด/วันที่บิล
-4. กด Confirm (ยืนยันบิล)</t>
+          <t>1. เปิด Accounting &gt; Vendors &gt; Bills &gt; New
+2. เลือก Vendor เดียวกับใน PO
+3. ที่ช่อง "Auto-Complete" เลือกเลขที่ PO — ระบบดึงบรรทัด/ยอดจาก PO มาให้อัตโนมัติ
+4. กรอก Bill Date
+5. กด Confirm</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vendor = "Demo Supplier - Global Stone Quarry"
+Auto-Complete = P00052</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>บิลสถานะ Posted ยอดตรงกับ PO (ตัวอย่างจริง: BILL/2026/09/0001, 163,710)</t>
+          <t>บิลสถานะ Posted ยอดตรงกับ PO บัญชีที่ลงถูกต้องเป็น "113110 Inventory - Stone Blocks (Raw)" ไม่ใช่บัญชี COGS ทั่วไป (ตัวอย่างจริง: BILL/2026/09/0002, 32,100.00)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -928,13 +948,13 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
-สินค้า = Bianco Sardo Granite - Block</t>
+          <t>ลูกค้า = "E2E Test Customer"
+สินค้า = SY-TST-Onyx-Rosa - Block</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>เพิ่มบรรทัดสำเร็จ ปุ่ม "Sell Whole Block" ปรากฏบนบรรทัดนั้น</t>
+          <t>เพิ่มบรรทัดสำเร็จ ปุ่ม "Sell Whole Block" ปรากฏบนบรรทัดนั้น (ราคาที่ขึ้นตอนนี้เป็นแค่ List Price เริ่มต้นของสินค้า ยังไม่ใช่ราคาจริงของก้อนนี้)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -956,7 +976,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>กด "Sell Whole Block" เลือกก้อนที่ซื้อมา</t>
+          <t>กด "Sell Whole Block" เลือกก้อนที่ซื้อมา — ราคาคำนวณอัตโนมัติ</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -967,18 +987,18 @@
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>1. กดปุ่ม "Sell Whole Block" บนบรรทัด
-2. หน้าต่าง "Select Block" เลือก Block ที่ซื้อไว้ (เช่น BLK-26-0016)
+2. หน้าต่าง "Select Block" เลือก Block ที่ซื้อไว้ (เช่น BLK-26-0068)
 3. กด "Confirm Selection"</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>เลือก Block = BLK-26-0016</t>
+          <t>เลือก Block = BLK-26-0068</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>บรรทัด SO ปรับจำนวนเป็น CBM ทั้งหมดของก้อนนั้นอัตโนมัติ (8.5) ราคาต่อหน่วยคำนวณจากต้นทุน/CBM ของก้อน (ตัวอย่างจริง: ราคาต่อหน่วย 25,000, ยอดรวมบรรทัด 212,500)</t>
+          <t>บรรทัด SO ปรับจำนวนเป็น CBM ทั้งหมดของก้อนนั้นอัตโนมัติ (2.00) ราคาต่อหน่วยเปลี่ยนเป็น 17,500.00 ทันที (จาก Sales Price / CBM ของก้อน ไม่ใช่ราคาที่พิมพ์ไว้ก่อนหน้า) ยอดรวมบรรทัด 35,000.00</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -986,7 +1006,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>✨ ใหม่ (2026-09-09): เดิม Unit Price ต้องพิมพ์เองหลังเลือกก้อน ตอนนี้ระบบดึง "Sales Price / CBM" ของก้อนนั้นมาใส่ให้อัตโนมัติทันทีที่กด Confirm Selection — พิมพ์ราคาอื่นทับไว้ก่อนก็ได้ ระบบจะเขียนทับด้วยราคาจริงของก้อนเสมอ</t>
+        </is>
+      </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -1020,7 +1044,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นให้อัตโนมัติ 1 ใบ (ตัวอย่างจริง: S00085 → EG01/OUT/00043)</t>
+          <t>SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นให้อัตโนมัติ 1 ใบ (ตัวอย่างจริง: S00091 → EG01/OUT/00067)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1172,7 +1196,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Mode 1 ขายทั้งก้อนโดยไม่ผ่านการตัด/ผลิตใดๆ — ลูกค้าซื้อก้อนดิบทั้งก้อนไปทั้งดุ้น ไปต่อที่การจัดส่งได้เลย ขั้นตอนผลิตจะมีใน Mode 3 (Cut-to-Order)/Mode 5 (FG Production) เท่านั้น ซึ่งจะทำเป็นชุด test case แยกต่างหาก</t>
+          <t>Mode 1 ขายทั้งก้อนโดยไม่ผ่านการตัด/ผลิตใดๆ — ลูกค้าซื้อก้อนดิบทั้งก้อนไปทั้งดุ้น ไปต่อที่การจัดส่งได้เลย ขั้นตอนผลิตจะมีใน Mode 3 (Cut-to-Order)/Mode 5 (FG Production) เท่านั้น</t>
         </is>
       </c>
       <c r="I4" s="7" t="n"/>
@@ -1308,7 +1332,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>เห็นใบส่งของสถานะ "Ready"/"Waiting" สินค้า 1 บรรทัด จำนวนตรงกับ SO (8.5 m³)</t>
+          <t>เห็นใบส่งของสถานะ "Ready" สินค้า 1 บรรทัด จำนวนตรงกับ SO (2.00 m³)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1350,7 +1374,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>ใบส่งของเปลี่ยนสถานะเป็น Done — Block ก้อนนั้นหายจากสต๊อกที่ขายได้ (Available) แล้ว</t>
+          <t>ใบส่งของเปลี่ยนสถานะเป็น Done (ตัวอย่างจริง: EG01/OUT/00067) — Block ก้อนนั้นหายจากสต๊อกที่ขายได้ (Available) แล้ว</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1378,7 +1402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1483,7 +1507,7 @@
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>1. เปิด Sale Order &gt; กด "Create Invoice"
-2. เลือก "Regular invoice" &gt; Create Draft Invoice
+2. เลือก "Regular invoice" &gt; Create Draft
 3. เปิดใบแจ้งหนี้ &gt; กด Confirm</t>
         </is>
       </c>
@@ -1494,7 +1518,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT (ตัวอย่างจริง: INV/2026/00009, 227,375)</t>
+          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT (ตัวอย่างจริง: INV/2026/00003, 37,450.00)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1526,7 +1550,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Vendor Bill &gt; กด smart button "Journal Items"</t>
+          <t>1. เปิด Vendor Bill &gt; แท็บ "Journal Items"</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1536,7 +1560,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>เห็น 3 บรรทัด: เดบิต Inventory - Stone Blocks (ยอดสินค้าก่อน VAT), เดบิต Input VAT, เครดิต Trade Payables (ยอดรวม) — ตัวอย่างจริง: 153,000 / 10,710 / 163,710</t>
+          <t>เห็น 3 บรรทัด: เดบิต 113110 Inventory - Stone Blocks (ยอดสินค้าก่อน VAT), เดบิต 114200 Input VAT, เครดิต 212100 Trade Payables (ยอดรวม) — ตัวอย่างจริง: 30,000 / 2,100 / 32,100 บัญชีถูกต้องตรงตัว ไม่ใช่บัญชี COGS ทั่วไป</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1568,7 +1592,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Customer Invoice &gt; กด smart button "Journal Items"</t>
+          <t>1. เปิด Customer Invoice &gt; แท็บ "Journal Items"</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1578,7 +1602,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>เห็น 5 บรรทัดบนใบแจ้งหนี้ใบเดียว: เครดิต Sales Revenue, เครดิต Output VAT, เดบิต Trade Receivables (รวม), และคู่ COGS/Inventory ที่ระบบแนบมาด้วยอัตโนมัติ (เดบิต COGS / เครดิต Inventory) — ตัวอย่างจริง: รายได้ 212,500 / VAT 14,875 / ลูกหนี้ 227,375 / COGS-Inventory คู่ละ 153,000.08</t>
+          <t>เห็น 5 บรรทัดบนใบแจ้งหนี้ใบเดียว: เครดิต 411110 Sales Revenue - Block Direct Sale (Mode 1), เดบิต 113110 Inventory (ตัดออก), เดบิต 511110 COGS - Block Direct Sale (Mode 1), เครดิต 213200 Output VAT, เดบิต 112100 Trade Receivables — ตัวอย่างจริง: รายได้ 35,000 / COGS-Inventory คู่ละ 30,000 / VAT 2,450 / ลูกหนี้ 37,450 (ยอดรวมสมดุล 67,450 = 67,450)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1600,7 +1624,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ตรวจว่าต้นทุนขาย (COGS) ถูกบันทึกซ้ำหรือไม่ — known issue</t>
+          <t>ตรวจว่าต้นทุนขาย (COGS) ถูกบันทึกซ้ำหรือไม่</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1611,8 +1635,7 @@
       <c r="D7" s="7" t="inlineStr">
         <is>
           <t>1. เปิด Accounting &gt; Journal Entries
-2. ค้นหา entry ที่มี Reference ตรงกับเลขที่ใบส่งของ (เช่น EG01/OUT/00043)
-3. เปิดดูรายละเอียดบรรทัด</t>
+2. ค้นหา entry ที่มี Reference ตรงกับเลขที่ใบส่งของ (เช่น EG01/OUT/00067)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1622,7 +1645,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>(พฤติกรรมที่พบจริงตอนนี้ ยังไม่ใช่ผลที่ถูกต้อง) เห็นคู่ COGS/Inventory ซ้ำอีกชุดในบัญชีคนละตัวจากข้อ 11 — ควรแจ้งทีมพัฒนาให้ตรวจสอบ ไม่ควรถือว่าผ่านการทดสอบจนกว่าจะยืนยันว่าไม่ใช่การนับซ้ำจริง</t>
+          <t>ไม่พบ Journal Entry แยกต่างหากสำหรับใบส่งของนี้เลย — COGS/Inventory มีบันทึกอยู่ที่เดียวคือในใบแจ้งหนี้ (INV/2026/00003) ไม่มีการนับซ้ำ</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1632,7 +1655,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>⚠️ พบจริงจากการทดสอบ (2026-09-06): เปิด Journal Entry ที่แยกต่างหากจากใบส่งของ (ชื่อขึ้นต้น STJ) จะเห็นคู่ COGS/Inventory อีกชุดหนึ่ง มูลค่าเท่ากันเป๊ะกับที่เห็นในใบแจ้งหนี้ (TC-E2E-M1-11) แต่ใช้บัญชีคนละตัว (511100 "Cost of Goods Sold" ธรรมดา แทนที่จะเป็น 511110 "COGS - Block Direct Sale (Mode 1)") — เช็คย้อนกลับไปที่ข้อมูลอ้างอิงเก่าของ session ก่อนหน้า (INV/2026/00008) ก็เจอรูปแบบเดียวกัน แปลว่าไม่ใช่บั๊กใหม่ แต่เป็นปัญหาที่มีอยู่แล้วและไม่เคยถูกจับได้มาก่อน ต้องส่งให้ทีม dev ตรวจว่าต้นทุนขายจริงถูกนับซ้ำสองครั้งในบัญชีหรือไม่</t>
+          <t>✅ ปิดเคสแล้ว — ตรวจซ้ำด้วย fixture ใหม่ (2026-09-09) ยืนยันว่าการแก้ไข ADR-054/055 (session ก่อนหน้า) ยังใช้ได้ดี: ไม่มี Journal Entry แยกต่างหากจากใบส่งของอีกต่อไป (เดิมมีปัญหาชื่อขึ้นต้น STJ ซ้ำกับใบแจ้งหนี้) — Delivery ไม่สร้าง Journal Entry ของตัวเองแล้ว COGS มีบันทึกอยู่ที่เดียวคือในใบแจ้งหนี้ (TC-E2E-M1-11)</t>
         </is>
       </c>
       <c r="I7" s="7" t="n"/>
@@ -1640,49 +1663,338 @@
       <c r="K7" s="7" t="n"/>
       <c r="L7" s="7" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>E6. สรุปกำไร (Gross Margin) — สรุปเทียบกำไรขั้นต้นของทั้งเรื่อง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>TC-E2E-M1-13</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>สรุปเทียบกำไรขั้นต้น (Gross Margin) ของรายการนี้</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>ทำ TC-E2E-M1-11 เสร็จแล้ว</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>1. คำนวณเอง: รายได้ (ไม่รวม VAT) ลบ ต้นทุนขาย (COGS)
-2. เทียบกับตัวเลขที่ระบบโชว์ (เช่นใน Analytic/Reporting ถ้ามี)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>รายได้ = 212,500
-COGS (นับครั้งเดียว) = 153,000.08</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น = 59,499.92 — ใช้ตัวเลขนี้เป็นฐานเทียบ ถ้า TC-E2E-M1-12 ยืนยันว่ามีการนับ COGS ซ้ำจริง กำไรที่ระบบสรุปในรายงานภาพรวมอาจต่ำกว่าความเป็นจริง ต้องระวังตอนอ่านรายงาน</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>1. คำนวณเอง: รายได้ (ไม่รวม VAT) ลบ ต้นทุนขาย (COGS)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>รายได้ = 35,000
+COGS (นับครั้งเดียว) = 30,000</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น = 5,000.00 (35,000 − 30,000) — ตัวเลขนี้ตรงกับที่เห็นในใบแจ้งหนี้ TC-E2E-M1-11 พอดี ไม่มี COGS ซ้ำมากวนตัวเลข</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>E7. ต้นทุนแยกตามมิติ (Cost-by-Material Analytics) — Analytic-Architecture ใหม่ 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M1-14</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ตรวจว่า Analytic Account ทั้ง 3 มิติติดมาอัตโนมัติบนบรรทัด SO</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M1-06 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Sale Order ที่ confirm แล้ว
+2. ที่ตาราง Order Lines กดไอคอนตั้งค่าคอลัมน์ (มุมขวาบนตาราง) เปิดคอลัมน์ "Analytic Distribution"</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>เห็น 2 ป้ายบนบรรทัดเดียว: "Marble | SY-TST-Onyx-Rosa" (หมวดวัสดุ+วัสดุ) และ "BLK-26-0068" (ก้อนนี้โดยเฉพาะ) — ไม่ต้องตั้งค่าเอง ระบบแท็กให้ตั้งแต่กด Sell Whole Block</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>✨ ใหม่ (2026-09-09): ทุกบรรทัดที่ผูกกับ Block จะถูกแท็กเข้า 3 มิติพร้อมกันโดยอัตโนมัติ — Block (ก้อนนี้โดยเฉพาะ), หมวดวัสดุ (เช่น Marble ใช้ร่วมกันได้ทุก Marble), และวัสดุ (เฉพาะ SY-TST-Onyx-Rosa) ไม่ต้องพิมพ์เอง ทำให้ดูกำไร/ต้นทุนแยกได้ทั้งรายก้อน รายหมวดวัสดุ หรือรายวัสดุเป๊ะๆ</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M1-15</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ตรวจว่า Analytic Account เดียวกันติดมาถึงบัญชีจริงด้วย ไม่ใช่แค่บนหน้าจอขาย</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M1-11 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Vendor Bill หรือ Customer Invoice &gt; แท็บ Journal Items
+2. ดูคอลัมน์ "Analytic Distribution"</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>ทุกบรรทัดบัญชี (Inventory, COGS, Revenue) มีป้าย Analytic เดียวกันติดมาด้วย — ต้นทุน/รายได้ก้อนนี้ดึงแยกได้ทันทีจากรายงาน Analytic โดยไม่ต้องรอบัญชีมาแปะป้ายย้อนหลัง</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
